--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_aysen.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_aysen.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>34.18414772013566</v>
+      </c>
+      <c r="C2">
         <v>21.33902776033162</v>
-      </c>
-      <c r="C2">
-        <v>34.18414772013566</v>
       </c>
       <c r="D2">
         <v>4.686249117023782</v>
       </c>
       <c r="E2">
-        <v>13.72080250702678</v>
+        <v>21.98009885956127</v>
       </c>
       <c r="F2">
         <v>64.29909863341194</v>
       </c>
       <c r="G2">
-        <v>21.98009885956127</v>
+        <v>13.72080250702678</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>33.48115299334812</v>
+      </c>
+      <c r="C3">
         <v>40.79822616407982</v>
-      </c>
-      <c r="C3">
-        <v>33.48115299334812</v>
       </c>
       <c r="D3">
         <v>2.451086956521739</v>
       </c>
       <c r="E3">
-        <v>23.40966921119592</v>
+        <v>19.21119592875318</v>
       </c>
       <c r="F3">
         <v>57.37913486005088</v>
       </c>
       <c r="G3">
-        <v>19.21119592875318</v>
+        <v>23.40966921119592</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>34.07606159589361</v>
+      </c>
+      <c r="C4">
         <v>20.99860009332711</v>
-      </c>
-      <c r="C4">
-        <v>34.07606159589361</v>
       </c>
       <c r="D4">
         <v>4.762222222222222</v>
       </c>
       <c r="E4">
-        <v>13.54096140825999</v>
+        <v>21.97397126307079</v>
       </c>
       <c r="F4">
         <v>64.48506732866923</v>
       </c>
       <c r="G4">
-        <v>21.97397126307079</v>
+        <v>13.54096140825999</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>35.11576626240353</v>
+      </c>
+      <c r="C5">
         <v>20.56229327453142</v>
-      </c>
-      <c r="C5">
-        <v>35.11576626240353</v>
       </c>
       <c r="D5">
         <v>4.863270777479893</v>
       </c>
       <c r="E5">
-        <v>13.20821529745043</v>
+        <v>22.55665722379604</v>
       </c>
       <c r="F5">
         <v>64.23512747875354</v>
       </c>
       <c r="G5">
-        <v>22.55665722379603</v>
+        <v>13.20821529745043</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>34.41860465116279</v>
+      </c>
+      <c r="C6">
         <v>17.48837209302325</v>
-      </c>
-      <c r="C6">
-        <v>34.41860465116279</v>
       </c>
       <c r="D6">
         <v>5.718085106382978</v>
       </c>
       <c r="E6">
-        <v>11.51255358236375</v>
+        <v>22.6576852418861</v>
       </c>
       <c r="F6">
         <v>65.82976117575015</v>
       </c>
       <c r="G6">
-        <v>22.6576852418861</v>
+        <v>11.51255358236375</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>33.57695614789338</v>
+      </c>
+      <c r="C7">
         <v>24.59157351676698</v>
-      </c>
-      <c r="C7">
-        <v>33.57695614789338</v>
       </c>
       <c r="D7">
         <v>4.066433566433567</v>
       </c>
       <c r="E7">
-        <v>15.54770318021201</v>
+        <v>21.22859472682794</v>
       </c>
       <c r="F7">
         <v>63.22370209296005</v>
       </c>
       <c r="G7">
-        <v>21.22859472682794</v>
+        <v>15.54770318021201</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>42.10526315789473</v>
+      </c>
+      <c r="C8">
         <v>19.39058171745152</v>
-      </c>
-      <c r="C8">
-        <v>42.10526315789473</v>
       </c>
       <c r="D8">
         <v>5.157142857142857</v>
       </c>
       <c r="E8">
+        <v>26.07204116638079</v>
+      </c>
+      <c r="F8">
+        <v>61.92109777015437</v>
+      </c>
+      <c r="G8">
         <v>12.00686106346484</v>
-      </c>
-      <c r="F8">
-        <v>61.92109777015438</v>
-      </c>
-      <c r="G8">
-        <v>26.07204116638079</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>40.92307692307692</v>
+      </c>
+      <c r="C9">
         <v>15.07692307692308</v>
-      </c>
-      <c r="C9">
-        <v>40.92307692307692</v>
       </c>
       <c r="D9">
         <v>6.63265306122449</v>
       </c>
       <c r="E9">
-        <v>9.664694280078894</v>
+        <v>26.232741617357</v>
       </c>
       <c r="F9">
-        <v>64.1025641025641</v>
+        <v>64.10256410256412</v>
       </c>
       <c r="G9">
-        <v>26.232741617357</v>
+        <v>9.664694280078896</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>29.03225806451613</v>
+      </c>
+      <c r="C10">
         <v>31.41528625399593</v>
-      </c>
-      <c r="C10">
-        <v>29.03225806451613</v>
       </c>
       <c r="D10">
         <v>3.183163737280296</v>
       </c>
       <c r="E10">
-        <v>19.57978627060315</v>
+        <v>18.09454808911429</v>
       </c>
       <c r="F10">
         <v>62.32566564028256</v>
       </c>
       <c r="G10">
-        <v>18.09454808911429</v>
+        <v>19.57978627060315</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>31.19718309859155</v>
+      </c>
+      <c r="C11">
         <v>41.76056338028169</v>
-      </c>
-      <c r="C11">
-        <v>31.19718309859155</v>
       </c>
       <c r="D11">
         <v>2.39460370994941</v>
       </c>
       <c r="E11">
-        <v>24.14495114006515</v>
+        <v>18.03745928338762</v>
       </c>
       <c r="F11">
         <v>57.81758957654723</v>
       </c>
       <c r="G11">
-        <v>18.03745928338762</v>
+        <v>24.14495114006515</v>
       </c>
     </row>
   </sheetData>
